--- a/DCA_prep-executions/DCA_Execution_SLATE_10-07-2026_V1.xlsx
+++ b/DCA_prep-executions/DCA_Execution_SLATE_10-07-2026_V1.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Alanl\Documents\GitHub\Stock_Picker\DCA_prep-executions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C976B005-F1A4-4A40-B9FF-72E1D9A153E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{57BD93E4-EDA0-4C89-AFE8-B073BECE7F17}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="21710" yWindow="630" windowWidth="16580" windowHeight="19590" xr2:uid="{81535BC7-C0A6-0A4F-99A4-E8B5751AB3B7}"/>
   </bookViews>
   <sheets>
-    <sheet name="DCA Slate TEMPLATE" sheetId="1" r:id="rId1"/>
+    <sheet name="DCA_Slate_10-07-2026" sheetId="1" r:id="rId1"/>
+    <sheet name="DCA Slate TEMPLATE" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="29">
   <si>
     <t>TICKER</t>
   </si>
@@ -62,9 +63,6 @@
     <t>SLB</t>
   </si>
   <si>
-    <t>ABT</t>
-  </si>
-  <si>
     <t>DCA SLATE</t>
   </si>
   <si>
@@ -95,9 +93,6 @@
     <t>FID</t>
   </si>
   <si>
-    <t>~ $</t>
-  </si>
-  <si>
     <t>~ Price</t>
   </si>
   <si>
@@ -129,6 +124,9 @@
   </si>
   <si>
     <t>VMFXX</t>
+  </si>
+  <si>
+    <t>[DATE]</t>
   </si>
 </sst>
 </file>
@@ -641,7 +639,42 @@
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="16">
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="FF9C0006"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <color rgb="FF9C0006"/>
@@ -1061,25 +1094,25 @@
         <v>46302</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C1" s="1"/>
       <c r="G1" s="27" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H1" s="28">
         <v>45000</v>
       </c>
       <c r="I1" s="43" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="15" t="s">
         <v>26</v>
-      </c>
-      <c r="B2" s="15" t="s">
-        <v>28</v>
       </c>
       <c r="C2" s="16"/>
       <c r="D2" s="16"/>
@@ -1093,8 +1126,8 @@
       <c r="B3" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="C3" s="3" t="s">
-        <v>18</v>
+      <c r="C3" s="35" t="s">
+        <v>19</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>1</v>
@@ -1103,25 +1136,25 @@
         <v>2</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G3" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H3" s="18" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A4" s="26"/>
       <c r="B4" s="29" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C4" s="36" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D4" s="38" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E4" s="5">
         <v>11408.02</v>
@@ -1144,11 +1177,11 @@
     <row r="5" spans="1:9" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A5" s="26"/>
       <c r="B5" s="4" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C5" s="36"/>
       <c r="D5" s="38" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E5" s="5">
         <v>9000</v>
@@ -1173,7 +1206,7 @@
       <c r="B6" s="4"/>
       <c r="C6" s="36"/>
       <c r="D6" s="38" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="6"/>
@@ -1194,7 +1227,7 @@
       <c r="B7" s="4"/>
       <c r="C7" s="36"/>
       <c r="D7" s="38" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="6"/>
@@ -1215,7 +1248,7 @@
       <c r="B8" s="4"/>
       <c r="C8" s="36"/>
       <c r="D8" s="38" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="6"/>
@@ -1271,8 +1304,8 @@
       <c r="B12" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C12" s="3" t="s">
-        <v>18</v>
+      <c r="C12" s="35" t="s">
+        <v>19</v>
       </c>
       <c r="D12" s="9" t="s">
         <v>1</v>
@@ -1281,13 +1314,13 @@
         <v>2</v>
       </c>
       <c r="F12" s="9" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G12" s="9" t="s">
         <v>3</v>
       </c>
       <c r="H12" s="22" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="13" spans="1:9" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -1296,10 +1329,10 @@
         <v>6</v>
       </c>
       <c r="C13" s="37" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D13" s="38" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E13" s="5">
         <v>400</v>
@@ -1324,7 +1357,7 @@
       <c r="B14" s="30"/>
       <c r="C14" s="37"/>
       <c r="D14" s="38" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E14" s="5"/>
       <c r="F14" s="6"/>
@@ -1345,7 +1378,7 @@
       <c r="B15" s="30"/>
       <c r="C15" s="37"/>
       <c r="D15" s="38" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E15" s="5"/>
       <c r="F15" s="6"/>
@@ -1366,7 +1399,7 @@
       <c r="B16" s="4"/>
       <c r="C16" s="37"/>
       <c r="D16" s="38" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E16" s="5"/>
       <c r="F16" s="6"/>
@@ -1387,7 +1420,7 @@
       <c r="B17" s="4"/>
       <c r="C17" s="37"/>
       <c r="D17" s="38" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="E17" s="5"/>
       <c r="F17" s="6"/>
@@ -1424,10 +1457,10 @@
     </row>
     <row r="21" spans="1:9" ht="20" x14ac:dyDescent="0.35">
       <c r="A21" s="25" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B21" s="15" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C21" s="16"/>
       <c r="D21" s="16"/>
@@ -1442,7 +1475,7 @@
         <v>0</v>
       </c>
       <c r="C22" s="35" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>1</v>
@@ -1451,25 +1484,25 @@
         <v>2</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G22" s="3" t="s">
         <v>3</v>
       </c>
       <c r="H22" s="18" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A23" s="26"/>
       <c r="B23" s="29" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C23" s="36" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D23" s="38" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E23" s="5">
         <v>24366.94</v>
@@ -1492,13 +1525,13 @@
     <row r="24" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A24" s="26"/>
       <c r="B24" s="4" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C24" s="36" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="D24" s="38" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E24" s="5">
         <v>30</v>
@@ -1523,7 +1556,7 @@
       <c r="B25" s="4"/>
       <c r="C25" s="36"/>
       <c r="D25" s="38" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E25" s="5"/>
       <c r="F25" s="6"/>
@@ -1544,7 +1577,7 @@
       <c r="B26" s="4"/>
       <c r="C26" s="36"/>
       <c r="D26" s="38" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E26" s="5"/>
       <c r="F26" s="6"/>
@@ -1565,7 +1598,7 @@
       <c r="B27" s="4"/>
       <c r="C27" s="36"/>
       <c r="D27" s="38" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E27" s="5"/>
       <c r="F27" s="6"/>
@@ -1621,8 +1654,8 @@
       <c r="B31" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C31" s="3" t="s">
-        <v>18</v>
+      <c r="C31" s="35" t="s">
+        <v>19</v>
       </c>
       <c r="D31" s="9" t="s">
         <v>1</v>
@@ -1631,13 +1664,13 @@
         <v>2</v>
       </c>
       <c r="F31" s="9" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G31" s="9" t="s">
         <v>3</v>
       </c>
       <c r="H31" s="22" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="I31" s="8"/>
     </row>
@@ -1647,10 +1680,10 @@
         <v>5</v>
       </c>
       <c r="C32" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" s="38" t="s">
         <v>16</v>
-      </c>
-      <c r="D32" s="38" t="s">
-        <v>17</v>
       </c>
       <c r="E32" s="5">
         <v>100</v>
@@ -1672,12 +1705,10 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A33" s="26"/>
-      <c r="B33" s="30" t="s">
-        <v>6</v>
-      </c>
+      <c r="B33" s="30"/>
       <c r="C33" s="37"/>
       <c r="D33" s="38" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E33" s="5"/>
       <c r="F33" s="6"/>
@@ -1695,12 +1726,10 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A34" s="26"/>
-      <c r="B34" s="30" t="s">
-        <v>7</v>
-      </c>
+      <c r="B34" s="30"/>
       <c r="C34" s="37"/>
       <c r="D34" s="38" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E34" s="5"/>
       <c r="F34" s="6"/>
@@ -1721,7 +1750,7 @@
       <c r="B35" s="4"/>
       <c r="C35" s="37"/>
       <c r="D35" s="38" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E35" s="5"/>
       <c r="F35" s="6"/>
@@ -1742,7 +1771,7 @@
       <c r="B36" s="4"/>
       <c r="C36" s="37"/>
       <c r="D36" s="38" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E36" s="5"/>
       <c r="F36" s="6"/>
@@ -1773,7 +1802,7 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.35">
       <c r="G39" s="39" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="H39" s="42">
         <f>SUM(H9+H28)</f>
@@ -1782,7 +1811,7 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.35">
       <c r="G40" s="39" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="H40" s="42">
         <f>SUM(H18+H37)</f>
@@ -1791,7 +1820,7 @@
     </row>
     <row r="41" spans="1:9" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="G41" s="40" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="H41" s="41">
         <f>SUM(H28,H37)</f>
@@ -1804,7 +1833,7 @@
     </row>
     <row r="43" spans="1:9" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
       <c r="G43" s="40" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="H43" s="41">
         <f>(H1+(H18+H37))</f>
@@ -1822,7 +1851,792 @@
     <mergeCell ref="B30:H30"/>
   </mergeCells>
   <conditionalFormatting sqref="H32:H36">
-    <cfRule type="cellIs" dxfId="8" priority="9" operator="lessThan">
+    <cfRule type="cellIs" dxfId="15" priority="9" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H41">
+    <cfRule type="cellIs" dxfId="12" priority="6" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H37">
+    <cfRule type="cellIs" dxfId="11" priority="5" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H13:H17">
+    <cfRule type="cellIs" dxfId="10" priority="4" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H18">
+    <cfRule type="cellIs" dxfId="9" priority="3" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="G32:G36">
+    <cfRule type="cellIs" dxfId="8" priority="2" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="H43">
+    <cfRule type="cellIs" dxfId="7" priority="1" operator="lessThan">
+      <formula>0</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A5A65E2A-6C20-4B54-9280-CE203577EC92}">
+  <dimension ref="A1:I44"/>
+  <sheetFormatPr defaultColWidth="10.83203125" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="1" max="1" width="15.5" style="2" customWidth="1"/>
+    <col min="2" max="3" width="10.83203125" style="2"/>
+    <col min="4" max="4" width="6.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="10.83203125" style="2"/>
+    <col min="7" max="7" width="12.58203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.9140625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="2.83203125" style="2" customWidth="1"/>
+    <col min="10" max="16384" width="10.83203125" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="30.5" thickBot="1" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="C1" s="1"/>
+      <c r="G1" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="H1" s="28">
+        <v>0</v>
+      </c>
+      <c r="I1" s="43" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A2" s="25" t="s">
+        <v>24</v>
+      </c>
+      <c r="B2" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C2" s="16"/>
+      <c r="D2" s="16"/>
+      <c r="E2" s="16"/>
+      <c r="F2" s="16"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="17"/>
+    </row>
+    <row r="3" spans="1:9" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="26"/>
+      <c r="B3" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H3" s="18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A4" s="26"/>
+      <c r="B4" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="D4" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="5"/>
+      <c r="F4" s="6">
+        <v>1</v>
+      </c>
+      <c r="G4" s="7">
+        <f>E4*F4</f>
+        <v>0</v>
+      </c>
+      <c r="H4" s="32">
+        <f>G4</f>
+        <v>0</v>
+      </c>
+      <c r="I4" s="31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A5" s="26"/>
+      <c r="B5" s="4"/>
+      <c r="C5" s="36"/>
+      <c r="D5" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="5"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="7">
+        <f t="shared" ref="G5:G8" si="0">E5*F5</f>
+        <v>0</v>
+      </c>
+      <c r="H5" s="32">
+        <f>H4+G5</f>
+        <v>0</v>
+      </c>
+      <c r="I5" s="31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A6" s="26"/>
+      <c r="B6" s="4"/>
+      <c r="C6" s="36"/>
+      <c r="D6" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="E6" s="5"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H6" s="32">
+        <f t="shared" ref="H6:H8" si="1">H5+G6</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A7" s="26"/>
+      <c r="B7" s="4"/>
+      <c r="C7" s="36"/>
+      <c r="D7" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="5"/>
+      <c r="F7" s="6"/>
+      <c r="G7" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H7" s="32">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I7" s="31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="26"/>
+      <c r="B8" s="4"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="5"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="7">
+        <f t="shared" si="0"/>
+        <v>0</v>
+      </c>
+      <c r="H8" s="32">
+        <f t="shared" si="1"/>
+        <v>0</v>
+      </c>
+      <c r="I8" s="31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="26"/>
+      <c r="B9" s="19"/>
+      <c r="C9" s="19"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="19"/>
+      <c r="G9" s="19"/>
+      <c r="H9" s="33">
+        <f>H8</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="26"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="20"/>
+    </row>
+    <row r="11" spans="1:9" ht="20" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="26"/>
+      <c r="B11" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C11" s="11"/>
+      <c r="D11" s="11"/>
+      <c r="E11" s="11"/>
+      <c r="F11" s="11"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="21"/>
+    </row>
+    <row r="12" spans="1:9" s="8" customFormat="1" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A12" s="26"/>
+      <c r="B12" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C12" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E12" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="F12" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G12" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="H12" s="22" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="26"/>
+      <c r="B13" s="30"/>
+      <c r="C13" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="E13" s="5"/>
+      <c r="F13" s="6"/>
+      <c r="G13" s="7">
+        <f>E13*F13</f>
+        <v>0</v>
+      </c>
+      <c r="H13" s="32">
+        <f>-G13</f>
+        <v>0</v>
+      </c>
+      <c r="I13" s="31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="26"/>
+      <c r="B14" s="30"/>
+      <c r="C14" s="37"/>
+      <c r="D14" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="E14" s="5"/>
+      <c r="F14" s="6"/>
+      <c r="G14" s="7">
+        <f t="shared" ref="G14:G17" si="2">E14*F14</f>
+        <v>0</v>
+      </c>
+      <c r="H14" s="32">
+        <f>H13-G14</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="26"/>
+      <c r="B15" s="30"/>
+      <c r="C15" s="37"/>
+      <c r="D15" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="E15" s="5"/>
+      <c r="F15" s="6"/>
+      <c r="G15" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H15" s="32">
+        <f t="shared" ref="H15:H17" si="3">H14-G15</f>
+        <v>0</v>
+      </c>
+      <c r="I15" s="31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="26"/>
+      <c r="B16" s="4"/>
+      <c r="C16" s="37"/>
+      <c r="D16" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="E16" s="5"/>
+      <c r="F16" s="6"/>
+      <c r="G16" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H16" s="32">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I16" s="31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="26"/>
+      <c r="B17" s="4"/>
+      <c r="C17" s="37"/>
+      <c r="D17" s="38" t="s">
+        <v>21</v>
+      </c>
+      <c r="E17" s="5"/>
+      <c r="F17" s="6"/>
+      <c r="G17" s="7">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+      <c r="H17" s="32">
+        <f t="shared" si="3"/>
+        <v>0</v>
+      </c>
+      <c r="I17" s="31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A18" s="23"/>
+      <c r="B18" s="24"/>
+      <c r="C18" s="24"/>
+      <c r="D18" s="24"/>
+      <c r="E18" s="24"/>
+      <c r="F18" s="24"/>
+      <c r="G18" s="24"/>
+      <c r="H18" s="34">
+        <f>H17</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" ht="15.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="14"/>
+    </row>
+    <row r="20" spans="1:9" ht="15.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="14"/>
+    </row>
+    <row r="21" spans="1:9" ht="20" x14ac:dyDescent="0.35">
+      <c r="A21" s="25" t="s">
+        <v>9</v>
+      </c>
+      <c r="B21" s="15" t="s">
+        <v>26</v>
+      </c>
+      <c r="C21" s="16"/>
+      <c r="D21" s="16"/>
+      <c r="E21" s="16"/>
+      <c r="F21" s="16"/>
+      <c r="G21" s="16"/>
+      <c r="H21" s="17"/>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A22" s="26"/>
+      <c r="B22" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="C22" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>1</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F22" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="G22" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="H22" s="18" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A23" s="26"/>
+      <c r="B23" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="36" t="s">
+        <v>14</v>
+      </c>
+      <c r="D23" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23" s="5"/>
+      <c r="F23" s="6">
+        <v>1</v>
+      </c>
+      <c r="G23" s="7">
+        <f>E23*F23</f>
+        <v>0</v>
+      </c>
+      <c r="H23" s="32">
+        <f>G23</f>
+        <v>0</v>
+      </c>
+      <c r="I23" s="31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A24" s="26"/>
+      <c r="B24" s="4"/>
+      <c r="C24" s="36"/>
+      <c r="D24" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" s="5"/>
+      <c r="F24" s="6"/>
+      <c r="G24" s="7">
+        <f t="shared" ref="G24:G27" si="4">E24*F24</f>
+        <v>0</v>
+      </c>
+      <c r="H24" s="32">
+        <f>H23+G24</f>
+        <v>0</v>
+      </c>
+      <c r="I24" s="31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A25" s="26"/>
+      <c r="B25" s="4"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="E25" s="5"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H25" s="32">
+        <f t="shared" ref="H25:H27" si="5">H24+G25</f>
+        <v>0</v>
+      </c>
+      <c r="I25" s="31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A26" s="26"/>
+      <c r="B26" s="4"/>
+      <c r="C26" s="36"/>
+      <c r="D26" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26" s="5"/>
+      <c r="F26" s="6"/>
+      <c r="G26" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H26" s="32">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I26" s="31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A27" s="26"/>
+      <c r="B27" s="4"/>
+      <c r="C27" s="36"/>
+      <c r="D27" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="E27" s="5"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="7">
+        <f t="shared" si="4"/>
+        <v>0</v>
+      </c>
+      <c r="H27" s="32">
+        <f t="shared" si="5"/>
+        <v>0</v>
+      </c>
+      <c r="I27" s="31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" ht="20" x14ac:dyDescent="0.4">
+      <c r="A28" s="26"/>
+      <c r="B28" s="19"/>
+      <c r="C28" s="19"/>
+      <c r="D28" s="19"/>
+      <c r="E28" s="19"/>
+      <c r="F28" s="19"/>
+      <c r="G28" s="19"/>
+      <c r="H28" s="33">
+        <f>H27</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A29" s="26"/>
+      <c r="B29" s="19"/>
+      <c r="C29" s="19"/>
+      <c r="D29" s="19"/>
+      <c r="E29" s="19"/>
+      <c r="F29" s="19"/>
+      <c r="G29" s="19"/>
+      <c r="H29" s="20"/>
+    </row>
+    <row r="30" spans="1:9" ht="20" x14ac:dyDescent="0.35">
+      <c r="A30" s="26"/>
+      <c r="B30" s="10" t="s">
+        <v>4</v>
+      </c>
+      <c r="C30" s="11"/>
+      <c r="D30" s="11"/>
+      <c r="E30" s="11"/>
+      <c r="F30" s="11"/>
+      <c r="G30" s="11"/>
+      <c r="H30" s="21"/>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A31" s="26"/>
+      <c r="B31" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C31" s="35" t="s">
+        <v>19</v>
+      </c>
+      <c r="D31" s="9" t="s">
+        <v>1</v>
+      </c>
+      <c r="E31" s="9" t="s">
+        <v>2</v>
+      </c>
+      <c r="F31" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="G31" s="9" t="s">
+        <v>3</v>
+      </c>
+      <c r="H31" s="22" t="s">
+        <v>18</v>
+      </c>
+      <c r="I31" s="8"/>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A32" s="26"/>
+      <c r="B32" s="30"/>
+      <c r="C32" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="D32" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="E32" s="5"/>
+      <c r="F32" s="6"/>
+      <c r="G32" s="32">
+        <f>E32*-F32</f>
+        <v>0</v>
+      </c>
+      <c r="H32" s="32">
+        <f>G32</f>
+        <v>0</v>
+      </c>
+      <c r="I32" s="31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A33" s="26"/>
+      <c r="B33" s="30"/>
+      <c r="C33" s="37"/>
+      <c r="D33" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="E33" s="5"/>
+      <c r="F33" s="6"/>
+      <c r="G33" s="32">
+        <f t="shared" ref="G33:G36" si="6">E33*F33</f>
+        <v>0</v>
+      </c>
+      <c r="H33" s="32">
+        <f>H32-G33</f>
+        <v>0</v>
+      </c>
+      <c r="I33" s="31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A34" s="26"/>
+      <c r="B34" s="30"/>
+      <c r="C34" s="37"/>
+      <c r="D34" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="E34" s="5"/>
+      <c r="F34" s="6"/>
+      <c r="G34" s="32">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H34" s="32">
+        <f t="shared" ref="H34:H36" si="7">H33-G34</f>
+        <v>0</v>
+      </c>
+      <c r="I34" s="31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A35" s="26"/>
+      <c r="B35" s="4"/>
+      <c r="C35" s="37"/>
+      <c r="D35" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="E35" s="5"/>
+      <c r="F35" s="6"/>
+      <c r="G35" s="32">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H35" s="32">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I35" s="31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A36" s="26"/>
+      <c r="B36" s="4"/>
+      <c r="C36" s="37"/>
+      <c r="D36" s="38" t="s">
+        <v>16</v>
+      </c>
+      <c r="E36" s="5"/>
+      <c r="F36" s="6"/>
+      <c r="G36" s="32">
+        <f t="shared" si="6"/>
+        <v>0</v>
+      </c>
+      <c r="H36" s="32">
+        <f t="shared" si="7"/>
+        <v>0</v>
+      </c>
+      <c r="I36" s="31" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="20" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A37" s="23"/>
+      <c r="B37" s="24"/>
+      <c r="C37" s="24"/>
+      <c r="D37" s="24"/>
+      <c r="E37" s="24"/>
+      <c r="F37" s="24"/>
+      <c r="G37" s="24"/>
+      <c r="H37" s="34">
+        <f>H36</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="G39" s="39" t="s">
+        <v>23</v>
+      </c>
+      <c r="H39" s="42">
+        <f>SUM(H9+H28)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="G40" s="39" t="s">
+        <v>22</v>
+      </c>
+      <c r="H40" s="42">
+        <f>SUM(H18+H37)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="G41" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="H41" s="41">
+        <f>SUM(H28,H37)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" ht="18.5" thickTop="1" x14ac:dyDescent="0.4">
+      <c r="G42" s="13"/>
+      <c r="H42" s="13"/>
+    </row>
+    <row r="43" spans="1:9" ht="18.5" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="G43" s="40" t="s">
+        <v>20</v>
+      </c>
+      <c r="H43" s="41">
+        <f>(H1+(H18+H37))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" ht="16" thickTop="1" x14ac:dyDescent="0.35"/>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A2:A17"/>
+    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B11:H11"/>
+    <mergeCell ref="A21:A36"/>
+    <mergeCell ref="B21:H21"/>
+    <mergeCell ref="B30:H30"/>
+  </mergeCells>
+  <conditionalFormatting sqref="H32:H36">
+    <cfRule type="cellIs" dxfId="6" priority="7" operator="lessThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
